--- a/_DOC/Ranking.xlsx
+++ b/_DOC/Ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IGOR\IGOR\IgorAyelloBorges\PROJETOS\FinancialMarketSimulatorRealData\_DOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8C5AF9B-E53C-4064-861C-7A3FBFC98AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE45B87E-FA25-40F6-A144-1C30F40DA941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92DB685F-C174-4FD2-BA6B-C724B0B14BBB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="30">
   <si>
     <t>ChatGPT</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Tempo para corrigir bugs de manutenção</t>
   </si>
   <si>
-    <t>Tempo</t>
-  </si>
-  <si>
     <t>Índice de dívida</t>
   </si>
   <si>
@@ -155,7 +152,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +171,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,20 +213,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -534,14 +544,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39B9AE4-77C4-496D-8DD4-1E41DC52F0A3}">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
     <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="53" customWidth="1"/>
+    <col min="4" max="4" width="58.85546875" customWidth="1"/>
+    <col min="5" max="5" width="53" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="30.28515625" customWidth="1"/>
     <col min="9" max="9" width="26.85546875" customWidth="1"/>
@@ -559,40 +570,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="3"/>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -613,7 +624,7 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -641,28 +652,28 @@
         <v>19</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="V2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="X2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -1040,11 +1051,755 @@
         <v>90</v>
       </c>
     </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <f>SUM(B11:E11)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:F15" si="1">SUM(B12:E12)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <f>SUM(B19:C19)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ref="D20:D23" si="2">SUM(B20:C20)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <f>SUM(B27:F27)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <f t="shared" ref="G28:G31" si="3">SUM(B28:F28)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <f>SUM(B35:E35)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36">
+        <f t="shared" ref="F36:F39" si="4">SUM(B36:E36)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <f>SUM(B43:F43)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <f t="shared" ref="G44:G47" si="5">SUM(B44:F44)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <f>SUM(B51:C51)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <f t="shared" ref="D52:D55" si="6">SUM(B52:C52)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="12">
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="M1:P1"/>
